--- a/out/Attention_Base_repeat_3_000001.xlsx
+++ b/out/Attention_Base_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-3.954107168743695</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001193065312565304</v>
+        <v>-3.997815127472859e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.05136982134831708</v>
+        <v>0.01721343121673911</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.102876950138943</v>
+        <v>0.03447280053031293</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1984696143434003</v>
+        <v>0.06650458816949664</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4485775096595639</v>
+        <v>0.1503125648032662</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06104985692368109</v>
+        <v>0.02045718412648821</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3719573825416039</v>
+        <v>0.1246381556901587</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01238767666281363</v>
+        <v>0.004148456709721048</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3355863526523777</v>
+        <v>0.1124485470426455</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01072792074593426</v>
+        <v>0.00359188650882811</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3446415392256791</v>
+        <v>0.1154797786514673</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.005242332886821498</v>
+        <v>0.001753444531976468</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3443867343550092</v>
+        <v>0.1153910713691376</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002499307198429786</v>
+        <v>0.0008342235435506434</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3441374487614098</v>
+        <v>0.1153042190055349</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001038274920498217</v>
+        <v>0.0003446140075095411</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3437117046466407</v>
+        <v>0.1151582599755391</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0007180561861544762</v>
+        <v>0.0002373048478682023</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3441088126854191</v>
+        <v>0.1152879391059952</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002971706140985907</v>
+        <v>9.61530627153065e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3439835392063703</v>
+        <v>0.1152426769818787</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001513521569990848</v>
+        <v>4.711738566636162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.3439894268605511</v>
+        <v>0.1152413221421279</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.64090981146772e-05</v>
+        <v>1.546969937155907e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3439505654376682</v>
+        <v>0.1152249393480336</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.878536241881745e-05</v>
+        <v>6.452665226717778e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3439511331256951</v>
+        <v>0.115221826699907</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.137548023346011e-05</v>
+        <v>6.467173218827975e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3439456258278603</v>
+        <v>0.1152166545182723</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.992384233967626e-06</v>
+        <v>-2.335871922010791e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3439396507308257</v>
+        <v>0.1152113294859275</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-1.771797027114496e-06</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.343933566571695</v>
+        <v>0.1152059684834257</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.346389286465195e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2363827036687994</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3439281795822265</v>
+        <v>0.115200823909492</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.36427134277522e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3439227950107928</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3439175231767418</v>
+        <v>0.1151954961151693</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.343917563032214</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3439176028876864</v>
+        <v>0.1151955758261138</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3439175949165919</v>
+        <v>0.1151955678550194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.343917754338481</v>
+        <v>0.1151957272769085</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3439180094135038</v>
+        <v>0.1151959823519313</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3439177623095754</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3439177224541032</v>
+        <v>0.1151956953925306</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3439177623095754</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3439178579627091</v>
+        <v>0.1151958309011366</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3439177941939533</v>
+        <v>0.1151957671323807</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.343917754338481</v>
+        <v>0.1151957272769085</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3439174833212695</v>
+        <v>0.115195456259697</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3439174036103247</v>
+        <v>0.1151953765487522</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3439174514368915</v>
+        <v>0.1151954243753189</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3439175710033085</v>
+        <v>0.115195543941736</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3439175550611196</v>
+        <v>0.1151955279995471</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3439175710033085</v>
+        <v>0.115195543941736</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3439175550611196</v>
+        <v>0.1151955279995471</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3439177623095754</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.343917977529126</v>
+        <v>0.1151959504675535</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.343917889847087</v>
+        <v>0.1151958627855144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3439178420205202</v>
+        <v>0.1151958149589477</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.343917889847087</v>
+        <v>0.1151958627855144</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3439177065119143</v>
+        <v>0.1151956794503417</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3439177144830087</v>
+        <v>0.1151956874214362</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3439177224541032</v>
+        <v>0.1151956953925306</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3439177702806699</v>
+        <v>0.1151957432190974</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3439178340494258</v>
+        <v>0.1151958069878533</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3439179456447481</v>
+        <v>0.1151959185831756</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3439179934713149</v>
+        <v>0.1151959664097424</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3439179536158426</v>
+        <v>0.1151959265542701</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3439178818759925</v>
+        <v>0.11519585481442</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3439180014424094</v>
+        <v>0.1151959743808368</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3439178420205202</v>
+        <v>0.1151958149589477</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.343917563032214</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3439175949165919</v>
+        <v>0.1151955678550194</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3439175789744029</v>
+        <v>0.1151955519128304</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3439174594079859</v>
+        <v>0.1151954323464134</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3439174195525136</v>
+        <v>0.1151953924909411</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.343917563032214</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3439176985408198</v>
+        <v>0.1151956714792473</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3439176825986309</v>
+        <v>0.1151956555370584</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3439176188298753</v>
+        <v>0.1151955917683027</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3439175152056473</v>
+        <v>0.1151954881440748</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3439173956392302</v>
+        <v>0.1151953685776577</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3439175152056473</v>
+        <v>0.1151954881440748</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.343917563032214</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3439175391189307</v>
+        <v>0.1151955120573582</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2363827036687994</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3439175470900251</v>
+        <v>0.1151955200284526</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000001.xlsx
+++ b/out/Attention_Base_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.954107168743695</v>
+        <v>-1.108934102311393</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.2363827036687994</v>
+        <v>-1.587847230587107</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.954107168743695</v>
+        <v>-1.587847230587107</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-3.954107168743695</v>
+        <v>-2.545673487138535</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-3.954107168743695</v>
+        <v>-1.387847230587107</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8363827036687994</v>
+        <v>-0.4300209740356794</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.5278052825157482</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001193065312565304</v>
+        <v>-0.000126773711825721</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.05136982134831708</v>
+        <v>0.05458507957534023</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.102876950138943</v>
+        <v>0.1093158322962425</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1984696143434003</v>
+        <v>0.2108902025195695</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4485775096595639</v>
+        <v>0.4766524021548235</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06104985692368109</v>
+        <v>0.06487151749650202</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3719573825416039</v>
+        <v>0.395236608578583</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01238767666281363</v>
+        <v>0.01316270689190945</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3355863526523777</v>
+        <v>0.3565894333806851</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01072792074593426</v>
+        <v>0.01139984694526939</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3446415392256791</v>
+        <v>0.3662114552439484</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.005242332886821498</v>
+        <v>0.005570641201111691</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3443867343550092</v>
+        <v>0.365941021903767</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002499307198429786</v>
+        <v>0.002656327527039978</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3441374487614098</v>
+        <v>0.3656764534609097</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001038274920498217</v>
+        <v>0.001103410014253975</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3437117046466407</v>
+        <v>0.365224447870807</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0007180561861544762</v>
+        <v>0.0007635848040660174</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3441088126854191</v>
+        <v>0.3656466466412989</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002971706140985907</v>
+        <v>0.0003158549377848575</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3439835392063703</v>
+        <v>0.3655139362093876</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001513521569990848</v>
+        <v>0.0001613747311656928</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.3439894268605511</v>
+        <v>0.3655204963439326</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.64090981146772e-05</v>
+        <v>6.008314671982883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3439505654376682</v>
+        <v>0.3654796176082099</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.878536241881745e-05</v>
+        <v>3.050326220282511e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3439511331256951</v>
+        <v>0.3654805162255845</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.137548023346011e-05</v>
+        <v>1.250482369783667e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3439456258278603</v>
+        <v>0.3654749744914227</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.992384233967626e-06</v>
+        <v>3.525209849565466e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3439396507308257</v>
+        <v>0.3654689343879193</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-1.771797027114496e-06</v>
+        <v>-1.310625173845138e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.343933566571695</v>
+        <v>0.3654627773373131</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3439281795822265</v>
+        <v>0.3654573903478447</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3439227950107928</v>
+        <v>0.3654520057764109</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3439175231767418</v>
+        <v>0.3654467339423599</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.343917563032214</v>
+        <v>0.3654467737978322</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3439176028876864</v>
+        <v>0.3654468136533044</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3439175949165919</v>
+        <v>0.36544680568221</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.343917754338481</v>
+        <v>0.3654469651040991</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.3654468694509657</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3439180094135038</v>
+        <v>0.365447220179122</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3439177623095754</v>
+        <v>0.3654469730751936</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3439177224541032</v>
+        <v>0.3654469332197213</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.3654468694509657</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.3654469411908158</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.3654468694509657</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3439177623095754</v>
+        <v>0.3654469730751936</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3439178579627091</v>
+        <v>0.3654470687283273</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3439177941939533</v>
+        <v>0.3654470049595714</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.343917754338481</v>
+        <v>0.3654469651040991</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.3654469411908158</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3439174833212695</v>
+        <v>0.3654466940868876</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3439174036103247</v>
+        <v>0.3654466143759428</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3439174514368915</v>
+        <v>0.3654466622025096</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3439175710033085</v>
+        <v>0.3654467817689266</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3439175550611196</v>
+        <v>0.3654467658267377</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3439175710033085</v>
+        <v>0.3654467817689266</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3439175550611196</v>
+        <v>0.3654467658267377</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.365446821624399</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.365446821624399</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.365446821624399</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3439177623095754</v>
+        <v>0.3654469730751936</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.343917977529126</v>
+        <v>0.3654471882947441</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.343917889847087</v>
+        <v>0.3654471006127051</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3439178420205202</v>
+        <v>0.3654470527861384</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.343917889847087</v>
+        <v>0.3654471006127051</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3439177065119143</v>
+        <v>0.3654469172775324</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3439177144830087</v>
+        <v>0.3654469252486269</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3439177224541032</v>
+        <v>0.3654469332197213</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.3654469411908158</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3439177304251976</v>
+        <v>0.3654469411908158</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3439177702806699</v>
+        <v>0.365446981046288</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3439178340494258</v>
+        <v>0.3654470448150439</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3439179456447481</v>
+        <v>0.3654471564103663</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3439179934713149</v>
+        <v>0.3654472042369331</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3439179536158426</v>
+        <v>0.3654471643814607</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3439178818759925</v>
+        <v>0.3654470926416106</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3439180014424094</v>
+        <v>0.3654472122080275</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3439178420205202</v>
+        <v>0.3654470527861384</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3439176108587808</v>
+        <v>0.365446821624399</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.343917563032214</v>
+        <v>0.3654467737978322</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3439175949165919</v>
+        <v>0.36544680568221</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.3654468694509657</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.3654468694509657</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3439175789744029</v>
+        <v>0.3654467897400211</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3439174594079859</v>
+        <v>0.365446670173604</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3439174195525136</v>
+        <v>0.3654466303181317</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.343917563032214</v>
+        <v>0.3654467737978322</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3439176985408198</v>
+        <v>0.3654469093064379</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3439176825986309</v>
+        <v>0.365446893364249</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.3654468694509657</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3439176188298753</v>
+        <v>0.3654468295954934</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3439175152056473</v>
+        <v>0.3654467259712655</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3439173956392302</v>
+        <v>0.3654466064048484</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3439175152056473</v>
+        <v>0.3654467259712655</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.343917563032214</v>
+        <v>0.3654467737978322</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3439176586853475</v>
+        <v>0.3654468694509657</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3439175391189307</v>
+        <v>0.3654467498845488</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2363827036687994</v>
+        <v>0.3278052825157481</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3439175470900251</v>
+        <v>0.3654467578556433</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000001.xlsx
+++ b/out/Attention_Base_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01364500634372234</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.108934102311393</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0007317308336496353</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.587847230587107</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002122035250067711</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.587847230587107</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.005802741274237633</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.005928315222263336</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001028286293148994</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003722149878740311</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.00568690337240696</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.005685549229383469</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.008143084123730659</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.008516674861311913</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.009816264733672142</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.009206240996718407</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.545673487138535</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.006694555282592773</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.545673487138535</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.003573548048734665</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.545673487138535</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0005697645246982574</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.545673487138535</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0001680981367826462</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.387847230587107</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0007362477481365204</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4300209740356794</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001356510445475578</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0007122699171304703</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0001517366617918015</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0003576762974262238</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001140780746936798</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002201559022068977</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002264039590954781</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002303652465343475</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002174409106373787</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5278052825157482</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001482810825109482</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001609131693840027</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.003238502889871597</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002670725807547569</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.003131033852696419</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002426205202937126</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001931823790073395</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001211382448673248</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001092109829187393</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001135203987360001</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.00131215900182724</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002887224778532982</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.005278173834085464</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01040253601968288</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02039476484060287</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.000126773711825721</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.05458507957534023</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.06259281933307648</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1093158322962425</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2108902025195695</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.1454411149024963</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4766524021548235</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06487151749650202</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.09293264150619507</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.395236608578583</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01316270689190945</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.07989377528429031</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3565894333806851</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01139984694526939</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.06107404083013535</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3662114552439484</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.005570641201111691</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.06790775060653687</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.365941021903767</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002656327527039978</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.06431745737791061</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3656764534609097</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001103410014253975</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.06189394742250443</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.365224447870807</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0007635848040660174</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.05967612564563751</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3656466466412989</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003158549377848575</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.07035936415195465</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3655139362093876</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001613747311656928</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.07212862372398376</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.3655204963439326</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>6.008314671982883e-05</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.05819988250732422</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3654796176082099</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.050326220282511e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.05708509683609009</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3654805162255845</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.250482369783667e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.04996413737535477</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3654749744914227</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.525209849565466e-06</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.05046027898788452</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3654689343879193</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-1.310625173845138e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.04918380826711655</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3654627773373131</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.346389286465195e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.04848746955394745</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3654573903478447</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.36427134277522e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0483228862285614</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3654520057764109</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.04536405205726624</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3654467339423599</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.04863431677222252</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3654467737978322</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.04437759146094322</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3654468136533044</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.04973985999822617</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.36544680568221</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0482315868139267</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3654469651040991</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.05683241039514542</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3654468694509657</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.05528105795383453</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.365447220179122</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.04916561394929886</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3654469730751936</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.05099406838417053</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3654469332197213</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.04545020312070847</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3654468694509657</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.04558082669973373</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3654469411908158</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.04464098811149597</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3654468694509657</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.07307695597410202</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3654469730751936</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.05967637151479721</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3654470687283273</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.04949291422963142</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3278052825157481</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3654470049595714</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.04553451389074326</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3654469651040991</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.04877627640962601</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3654469411908158</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.04360192269086838</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3654466940868876</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.04095636308193207</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3654466143759428</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.04125544428825378</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3654466622025096</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.04018861055374146</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3654467817689266</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.04155655577778816</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3654467658267377</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.04063982516527176</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3654467817689266</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.04132016748189926</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3654467658267377</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.04059401154518127</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.365446821624399</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.03803611919283867</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.365446821624399</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.04539615660905838</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.365446821624399</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0408632829785347</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3654469730751936</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.05105483531951904</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3654471882947441</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.04170820116996765</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3654471006127051</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.04154457896947861</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3654470527861384</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.0425555482506752</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3654471006127051</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03806626796722412</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3654469172775324</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0373818650841713</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3654469252486269</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0386563166975975</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3654469332197213</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.03605544194579124</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3654469411908158</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.03576696664094925</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3654469411908158</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.0421285554766655</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.365446981046288</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.04069343209266663</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3654470448150439</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.04234052821993828</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3654471564103663</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.03867629170417786</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3654472042369331</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.03967304527759552</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3654471643814607</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.04044425487518311</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3654470926416106</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.04064029455184937</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3654472122080275</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.04066971689462662</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3654470527861384</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.03565407171845436</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.365446821624399</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.03468776866793633</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3654467737978322</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.03314583376049995</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.36544680568221</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.03468188643455505</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3654468694509657</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03226931393146515</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3654468694509657</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.03156349062919617</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3654467897400211</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.03090854734182358</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.365446670173604</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.03060342185199261</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3654466303181317</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.03227300196886063</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3654467737978322</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0317472517490387</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3654469093064379</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0301547460258007</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.365446893364249</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.03021093644201756</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3654468694509657</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.02975434437394142</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3654468295954934</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.03054235503077507</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3654467259712655</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.03174252808094025</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3654466064048484</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.02925059758126736</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3654467259712655</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.03076345846056938</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3654467737978322</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.02892210148274899</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3654468694509657</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.02880667336285114</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3654467498845488</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.03088670969009399</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3278052825157481</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3654467578556433</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000001.xlsx
+++ b/out/Attention_Base_repeat_3_000001.xlsx
@@ -50234,7 +50234,7 @@
         <v>0.04536405205726624</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0.5237405445165164</v>
@@ -51029,7 +51029,7 @@
         <v>0.04863431677222252</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
         <v>0.523735623362795</v>
@@ -51824,7 +51824,7 @@
         <v>0.04437759146094322</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
         <v>0.5237356632182673</v>
@@ -52619,7 +52619,7 @@
         <v>0.04973985999822617</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0.5237356552471728</v>
@@ -53414,7 +53414,7 @@
         <v>0.0482315868139267</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0.5237358146690619</v>
@@ -55799,7 +55799,7 @@
         <v>0.04916561394929886</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
         <v>0.5237358226401564</v>
@@ -60569,7 +60569,7 @@
         <v>0.05967637151479721</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0.52373591829329</v>
